--- a/models/naat/data/lparametros.xlsx
+++ b/models/naat/data/lparametros.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PiaToolv2\models\naat\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asantoro\Desktop\PiaToolv2\models\naat\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB52068-A4A8-40C9-BDAA-B6625E25038E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="parametros" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">parametros!$A$1:$AE$831</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,8 +29,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -2358,7 +2357,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mmmm\ yyyy"/>
   </numFmts>
@@ -2942,7 +2941,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -36246,112 +36245,112 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I5" r:id="rId1"/>
-    <hyperlink ref="I6" r:id="rId2"/>
-    <hyperlink ref="I9" r:id="rId3"/>
-    <hyperlink ref="I10" r:id="rId4"/>
-    <hyperlink ref="I17" r:id="rId5"/>
-    <hyperlink ref="I18" r:id="rId6"/>
-    <hyperlink ref="I19" r:id="rId7"/>
-    <hyperlink ref="I20" r:id="rId8"/>
-    <hyperlink ref="I21" r:id="rId9"/>
-    <hyperlink ref="I24" r:id="rId10"/>
-    <hyperlink ref="I26" r:id="rId11"/>
-    <hyperlink ref="I31" r:id="rId12"/>
-    <hyperlink ref="I32" r:id="rId13"/>
-    <hyperlink ref="I38" r:id="rId14"/>
-    <hyperlink ref="I39" r:id="rId15"/>
-    <hyperlink ref="I40" r:id="rId16"/>
-    <hyperlink ref="I42" r:id="rId17"/>
-    <hyperlink ref="I43" r:id="rId18"/>
-    <hyperlink ref="I44" r:id="rId19"/>
-    <hyperlink ref="I45" r:id="rId20"/>
-    <hyperlink ref="I46" r:id="rId21"/>
-    <hyperlink ref="I53" r:id="rId22"/>
-    <hyperlink ref="I54" r:id="rId23"/>
-    <hyperlink ref="I55" r:id="rId24"/>
-    <hyperlink ref="I57" r:id="rId25"/>
-    <hyperlink ref="I58" r:id="rId26"/>
-    <hyperlink ref="I59" r:id="rId27"/>
-    <hyperlink ref="I60" r:id="rId28"/>
-    <hyperlink ref="I61" r:id="rId29"/>
-    <hyperlink ref="I63" r:id="rId30"/>
-    <hyperlink ref="I68" r:id="rId31"/>
-    <hyperlink ref="I69" r:id="rId32"/>
-    <hyperlink ref="I70" r:id="rId33"/>
-    <hyperlink ref="I72" r:id="rId34"/>
-    <hyperlink ref="I73" r:id="rId35"/>
-    <hyperlink ref="I74" r:id="rId36"/>
-    <hyperlink ref="I75" r:id="rId37"/>
-    <hyperlink ref="I76" r:id="rId38"/>
-    <hyperlink ref="I78" r:id="rId39"/>
-    <hyperlink ref="I83" r:id="rId40"/>
-    <hyperlink ref="I84" r:id="rId41"/>
-    <hyperlink ref="I85" r:id="rId42"/>
-    <hyperlink ref="I87" r:id="rId43"/>
-    <hyperlink ref="I88" r:id="rId44"/>
-    <hyperlink ref="I89" r:id="rId45"/>
-    <hyperlink ref="I90" r:id="rId46"/>
-    <hyperlink ref="I91" r:id="rId47"/>
-    <hyperlink ref="I93" r:id="rId48"/>
-    <hyperlink ref="I98" r:id="rId49"/>
-    <hyperlink ref="I99" r:id="rId50"/>
-    <hyperlink ref="I100" r:id="rId51"/>
-    <hyperlink ref="I102" r:id="rId52"/>
-    <hyperlink ref="I103" r:id="rId53"/>
-    <hyperlink ref="I104" r:id="rId54"/>
-    <hyperlink ref="I105" r:id="rId55"/>
-    <hyperlink ref="I106" r:id="rId56"/>
-    <hyperlink ref="I113" r:id="rId57"/>
-    <hyperlink ref="I114" r:id="rId58"/>
-    <hyperlink ref="I115" r:id="rId59"/>
-    <hyperlink ref="I117" r:id="rId60"/>
-    <hyperlink ref="I118" r:id="rId61"/>
-    <hyperlink ref="I119" r:id="rId62"/>
-    <hyperlink ref="I120" r:id="rId63"/>
-    <hyperlink ref="I121" r:id="rId64"/>
-    <hyperlink ref="I123" r:id="rId65"/>
-    <hyperlink ref="I128" r:id="rId66"/>
-    <hyperlink ref="I129" r:id="rId67"/>
-    <hyperlink ref="I130" r:id="rId68"/>
-    <hyperlink ref="I132" r:id="rId69"/>
-    <hyperlink ref="I133" r:id="rId70"/>
-    <hyperlink ref="I134" r:id="rId71"/>
-    <hyperlink ref="I135" r:id="rId72"/>
-    <hyperlink ref="I136" r:id="rId73"/>
-    <hyperlink ref="I138" r:id="rId74"/>
-    <hyperlink ref="I143" r:id="rId75"/>
-    <hyperlink ref="I144" r:id="rId76"/>
-    <hyperlink ref="I145" r:id="rId77"/>
-    <hyperlink ref="I147" r:id="rId78"/>
-    <hyperlink ref="I148" r:id="rId79"/>
-    <hyperlink ref="I149" r:id="rId80"/>
-    <hyperlink ref="I150" r:id="rId81"/>
-    <hyperlink ref="I151" r:id="rId82"/>
-    <hyperlink ref="I158" r:id="rId83"/>
-    <hyperlink ref="I159" r:id="rId84"/>
-    <hyperlink ref="I160" r:id="rId85"/>
-    <hyperlink ref="I162" r:id="rId86"/>
-    <hyperlink ref="I163" r:id="rId87"/>
-    <hyperlink ref="I164" r:id="rId88"/>
-    <hyperlink ref="I165" r:id="rId89"/>
-    <hyperlink ref="I166" r:id="rId90"/>
-    <hyperlink ref="I173" r:id="rId91"/>
-    <hyperlink ref="I174" r:id="rId92"/>
-    <hyperlink ref="I175" r:id="rId93"/>
-    <hyperlink ref="I177" r:id="rId94"/>
-    <hyperlink ref="I178" r:id="rId95"/>
-    <hyperlink ref="I179" r:id="rId96"/>
-    <hyperlink ref="I180" r:id="rId97"/>
-    <hyperlink ref="I181" r:id="rId98"/>
-    <hyperlink ref="I188" r:id="rId99"/>
-    <hyperlink ref="I189" r:id="rId100"/>
-    <hyperlink ref="I190" r:id="rId101"/>
-    <hyperlink ref="I192" r:id="rId102"/>
-    <hyperlink ref="I193" r:id="rId103"/>
-    <hyperlink ref="I194" r:id="rId104"/>
-    <hyperlink ref="I195" r:id="rId105"/>
-    <hyperlink ref="I196" r:id="rId106"/>
+    <hyperlink ref="I5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="I6" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="I9" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="I10" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="I17" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="I18" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="I19" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="I20" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="I21" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="I24" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="I26" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="I31" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="I32" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="I38" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="I39" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="I40" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="I42" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="I43" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="I44" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="I45" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="I46" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="I53" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="I54" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="I55" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="I57" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="I58" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="I59" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="I60" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="I61" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="I63" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="I68" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="I69" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="I70" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="I72" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="I73" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="I74" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="I75" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="I76" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="I78" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="I83" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="I84" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="I85" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="I87" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="I88" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="I89" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="I90" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="I91" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="I93" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="I98" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="I99" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="I100" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="I102" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="I103" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="I104" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="I105" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="I106" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="I113" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="I114" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="I115" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="I117" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="I118" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="I119" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="I120" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="I121" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="I123" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="I128" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="I129" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="I130" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="I132" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="I133" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="I134" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="I135" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="I136" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="I138" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="I143" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="I144" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="I145" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="I147" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="I148" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="I149" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="I150" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="I151" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="I158" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="I159" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="I160" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="I162" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="I163" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="I164" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="I165" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="I166" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="I173" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="I174" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="I175" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="I177" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="I178" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="I179" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="I180" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="I181" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="I188" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="I189" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="I190" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="I192" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="I193" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="I194" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="I195" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="I196" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId107"/>
@@ -36359,7 +36358,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -37495,8 +37494,8 @@
       <c r="C50" s="36" t="s">
         <v>297</v>
       </c>
-      <c r="D50" s="35" t="s">
-        <v>279</v>
+      <c r="D50" s="9" t="s">
+        <v>222</v>
       </c>
       <c r="E50" s="44">
         <v>2</v>
@@ -40602,7 +40601,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
